--- a/data/nzd0158/nzd0158.xlsx
+++ b/data/nzd0158/nzd0158.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L372"/>
+  <dimension ref="A1:L373"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16058,6 +16058,48 @@
       <c r="L372" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:05:44+00:00</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>381.83</v>
+      </c>
+      <c r="C373" t="n">
+        <v>379.68</v>
+      </c>
+      <c r="D373" t="n">
+        <v>382.19</v>
+      </c>
+      <c r="E373" t="n">
+        <v>380.91</v>
+      </c>
+      <c r="F373" t="n">
+        <v>377.93</v>
+      </c>
+      <c r="G373" t="n">
+        <v>371.06</v>
+      </c>
+      <c r="H373" t="n">
+        <v>367.41</v>
+      </c>
+      <c r="I373" t="n">
+        <v>368.32</v>
+      </c>
+      <c r="J373" t="n">
+        <v>367.07</v>
+      </c>
+      <c r="K373" t="n">
+        <v>376.19</v>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -16072,7 +16114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B386"/>
+  <dimension ref="A1:B387"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19935,6 +19977,16 @@
       </c>
       <c r="B386" t="n">
         <v>-0.43</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B387" t="n">
+        <v>0.55</v>
       </c>
     </row>
   </sheetData>
@@ -20103,28 +20155,28 @@
         <v>0.109</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1257507786832321</v>
+        <v>0.1252310128877793</v>
       </c>
       <c r="J2" t="n">
+        <v>372</v>
+      </c>
+      <c r="K2" t="n">
         <v>371</v>
       </c>
-      <c r="K2" t="n">
-        <v>370</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.04206284808053351</v>
+        <v>0.04196931216063438</v>
       </c>
       <c r="M2" t="n">
-        <v>3.450749441118535</v>
+        <v>3.444001373022762</v>
       </c>
       <c r="N2" t="n">
-        <v>18.97907564323625</v>
+        <v>18.9302602045264</v>
       </c>
       <c r="O2" t="n">
-        <v>4.356498094024173</v>
+        <v>4.350891886099492</v>
       </c>
       <c r="P2" t="n">
-        <v>379.4381180994504</v>
+        <v>379.4436966706539</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -20181,28 +20233,28 @@
         <v>0.1104</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05278127364899568</v>
+        <v>0.05302680762027757</v>
       </c>
       <c r="J3" t="n">
+        <v>372</v>
+      </c>
+      <c r="K3" t="n">
         <v>371</v>
       </c>
-      <c r="K3" t="n">
-        <v>370</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.01139695982836353</v>
+        <v>0.01157092347619915</v>
       </c>
       <c r="M3" t="n">
-        <v>2.771757179557453</v>
+        <v>2.765544675293188</v>
       </c>
       <c r="N3" t="n">
-        <v>12.73526555052375</v>
+        <v>12.70146111863853</v>
       </c>
       <c r="O3" t="n">
-        <v>3.568650382220671</v>
+        <v>3.563910930233601</v>
       </c>
       <c r="P3" t="n">
-        <v>377.8401368982489</v>
+        <v>377.8375016176021</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -20259,28 +20311,28 @@
         <v>0.1999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.05078511604998847</v>
+        <v>-0.0478635581741647</v>
       </c>
       <c r="J4" t="n">
+        <v>372</v>
+      </c>
+      <c r="K4" t="n">
         <v>371</v>
       </c>
-      <c r="K4" t="n">
-        <v>370</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.01255030119022504</v>
+        <v>0.01115437610657455</v>
       </c>
       <c r="M4" t="n">
-        <v>2.56884843163845</v>
+        <v>2.575045405991116</v>
       </c>
       <c r="N4" t="n">
-        <v>10.69421918298201</v>
+        <v>10.73936001889467</v>
       </c>
       <c r="O4" t="n">
-        <v>3.270201703715232</v>
+        <v>3.277096278551283</v>
       </c>
       <c r="P4" t="n">
-        <v>378.2682999897239</v>
+        <v>378.2369433310558</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -20337,28 +20389,28 @@
         <v>0.0883</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03356579810341264</v>
+        <v>0.0357549897502448</v>
       </c>
       <c r="J5" t="n">
+        <v>372</v>
+      </c>
+      <c r="K5" t="n">
         <v>371</v>
       </c>
-      <c r="K5" t="n">
-        <v>370</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.004288790840762502</v>
+        <v>0.004878530316499763</v>
       </c>
       <c r="M5" t="n">
-        <v>2.882182377179968</v>
+        <v>2.883632074295874</v>
       </c>
       <c r="N5" t="n">
-        <v>13.78503378077156</v>
+        <v>13.78940832104399</v>
       </c>
       <c r="O5" t="n">
-        <v>3.712820192356688</v>
+        <v>3.713409258490638</v>
       </c>
       <c r="P5" t="n">
-        <v>376.0745849435946</v>
+        <v>376.0510886658736</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -20415,28 +20467,28 @@
         <v>0.1058</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05990202910120553</v>
+        <v>0.06226448502523071</v>
       </c>
       <c r="J6" t="n">
+        <v>372</v>
+      </c>
+      <c r="K6" t="n">
         <v>371</v>
       </c>
-      <c r="K6" t="n">
-        <v>370</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.02045474266976355</v>
+        <v>0.02207970393084535</v>
       </c>
       <c r="M6" t="n">
-        <v>2.368627051471583</v>
+        <v>2.371879953517094</v>
       </c>
       <c r="N6" t="n">
-        <v>9.055843379901235</v>
+        <v>9.079799176590628</v>
       </c>
       <c r="O6" t="n">
-        <v>3.009292837179731</v>
+        <v>3.013270511685041</v>
       </c>
       <c r="P6" t="n">
-        <v>372.0871521076886</v>
+        <v>372.061796209508</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -20493,28 +20545,28 @@
         <v>0.0876</v>
       </c>
       <c r="I7" t="n">
-        <v>0.121748056435088</v>
+        <v>0.1230228061904929</v>
       </c>
       <c r="J7" t="n">
+        <v>372</v>
+      </c>
+      <c r="K7" t="n">
         <v>371</v>
       </c>
-      <c r="K7" t="n">
-        <v>370</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.0440195330714368</v>
+        <v>0.0451303235889825</v>
       </c>
       <c r="M7" t="n">
-        <v>3.229096017552256</v>
+        <v>3.22446927266331</v>
       </c>
       <c r="N7" t="n">
-        <v>16.96457602148104</v>
+        <v>16.93293107716891</v>
       </c>
       <c r="O7" t="n">
-        <v>4.118807597045659</v>
+        <v>4.114964286256797</v>
       </c>
       <c r="P7" t="n">
-        <v>365.536319144712</v>
+        <v>365.5226374397222</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -20571,28 +20623,28 @@
         <v>0.0589</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1213584523135733</v>
+        <v>-0.1205263196503963</v>
       </c>
       <c r="J8" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="K8" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L8" t="n">
-        <v>0.030513331742127</v>
+        <v>0.03027901683967249</v>
       </c>
       <c r="M8" t="n">
-        <v>3.906429332140519</v>
+        <v>3.900336939423952</v>
       </c>
       <c r="N8" t="n">
-        <v>24.89881815075211</v>
+        <v>24.8379722872074</v>
       </c>
       <c r="O8" t="n">
-        <v>4.989871556538516</v>
+        <v>4.983770890320642</v>
       </c>
       <c r="P8" t="n">
-        <v>369.1163245306931</v>
+        <v>369.1074515091232</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -20649,28 +20701,28 @@
         <v>0.0837</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.05759271003548339</v>
+        <v>-0.05719203484933316</v>
       </c>
       <c r="J9" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="K9" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01106661339771131</v>
+        <v>0.01097943567509596</v>
       </c>
       <c r="M9" t="n">
-        <v>2.836456130731638</v>
+        <v>2.831071490429261</v>
       </c>
       <c r="N9" t="n">
-        <v>15.77152883685364</v>
+        <v>15.73054337197717</v>
       </c>
       <c r="O9" t="n">
-        <v>3.97133841882729</v>
+        <v>3.966174904360267</v>
       </c>
       <c r="P9" t="n">
-        <v>369.1193829691613</v>
+        <v>369.1151105739933</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -20727,28 +20779,28 @@
         <v>0.076</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.05409761101424932</v>
+        <v>-0.05311871513128841</v>
       </c>
       <c r="J10" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="K10" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L10" t="n">
-        <v>0.006889058964471673</v>
+        <v>0.006681227487688179</v>
       </c>
       <c r="M10" t="n">
-        <v>3.630241165640748</v>
+        <v>3.626322562754534</v>
       </c>
       <c r="N10" t="n">
-        <v>22.44814724549297</v>
+        <v>22.39622546586588</v>
       </c>
       <c r="O10" t="n">
-        <v>4.737947577326386</v>
+        <v>4.732465051732118</v>
       </c>
       <c r="P10" t="n">
-        <v>366.7226751066891</v>
+        <v>366.712237150497</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -20805,28 +20857,28 @@
         <v>0.1273</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1357941030087829</v>
+        <v>-0.1365938293123805</v>
       </c>
       <c r="J11" t="n">
+        <v>372</v>
+      </c>
+      <c r="K11" t="n">
         <v>371</v>
       </c>
-      <c r="K11" t="n">
-        <v>370</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.06141236624842961</v>
+        <v>0.06242613298935873</v>
       </c>
       <c r="M11" t="n">
-        <v>3.150111358285561</v>
+        <v>3.145686741809387</v>
       </c>
       <c r="N11" t="n">
-        <v>14.85238393645179</v>
+        <v>14.81789282076567</v>
       </c>
       <c r="O11" t="n">
-        <v>3.853879076521705</v>
+        <v>3.849401618533154</v>
       </c>
       <c r="P11" t="n">
-        <v>381.2221441322556</v>
+        <v>381.2307274791533</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -20864,7 +20916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L372"/>
+  <dimension ref="A1:L373"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43903,6 +43955,68 @@
         </is>
       </c>
     </row>
+    <row r="373">
+      <c r="A373" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:05:44+00:00</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>-36.72668417821705,175.70209961322973</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>-36.72663859267189,175.70299688433477</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>-36.72655151518745,175.70388668051405</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>-36.72648830393771,175.7047765303035</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>-36.726419652729064,175.70566861364313</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>-36.726385215097295,175.706569077398</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>-36.726304951406476,175.7074608995577</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>-36.72616632466442,175.70833890664812</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>-36.72601828474763,175.70921958746396</t>
+        </is>
+      </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>-36.72583091411464,175.7100925496774</t>
+        </is>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0158/nzd0158.xlsx
+++ b/data/nzd0158/nzd0158.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L373"/>
+  <dimension ref="A1:L374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16098,6 +16098,48 @@
         <v>376.19</v>
       </c>
       <c r="L373" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B374" t="n">
+        <v>382.15</v>
+      </c>
+      <c r="C374" t="n">
+        <v>380.01</v>
+      </c>
+      <c r="D374" t="n">
+        <v>379.34</v>
+      </c>
+      <c r="E374" t="n">
+        <v>378.82</v>
+      </c>
+      <c r="F374" t="n">
+        <v>376.63</v>
+      </c>
+      <c r="G374" t="n">
+        <v>370.05</v>
+      </c>
+      <c r="H374" t="n">
+        <v>364.98</v>
+      </c>
+      <c r="I374" t="n">
+        <v>366.82</v>
+      </c>
+      <c r="J374" t="n">
+        <v>364.93</v>
+      </c>
+      <c r="K374" t="n">
+        <v>373.29</v>
+      </c>
+      <c r="L374" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -16114,7 +16156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B387"/>
+  <dimension ref="A1:B388"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19987,6 +20029,16 @@
       </c>
       <c r="B387" t="n">
         <v>0.55</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B388" t="n">
+        <v>-0.08</v>
       </c>
     </row>
   </sheetData>
@@ -20155,28 +20207,28 @@
         <v>0.109</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1252310128877793</v>
+        <v>0.12488654856879</v>
       </c>
       <c r="J2" t="n">
+        <v>373</v>
+      </c>
+      <c r="K2" t="n">
         <v>372</v>
       </c>
-      <c r="K2" t="n">
-        <v>371</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.04196931216063438</v>
+        <v>0.04199135049454916</v>
       </c>
       <c r="M2" t="n">
-        <v>3.444001373022762</v>
+        <v>3.436438295611768</v>
       </c>
       <c r="N2" t="n">
-        <v>18.9302602045264</v>
+        <v>18.88039948641866</v>
       </c>
       <c r="O2" t="n">
-        <v>4.350891886099492</v>
+        <v>4.345158165869069</v>
       </c>
       <c r="P2" t="n">
-        <v>379.4436966706539</v>
+        <v>379.4474070973187</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -20233,28 +20285,28 @@
         <v>0.1104</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05302680762027757</v>
+        <v>0.05344829856953776</v>
       </c>
       <c r="J3" t="n">
+        <v>373</v>
+      </c>
+      <c r="K3" t="n">
         <v>372</v>
       </c>
-      <c r="K3" t="n">
-        <v>371</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.01157092347619915</v>
+        <v>0.01182320753153432</v>
       </c>
       <c r="M3" t="n">
-        <v>2.765544675293188</v>
+        <v>2.760248378862429</v>
       </c>
       <c r="N3" t="n">
-        <v>12.70146111863853</v>
+        <v>12.66885517639256</v>
       </c>
       <c r="O3" t="n">
-        <v>3.563910930233601</v>
+        <v>3.559333529804781</v>
       </c>
       <c r="P3" t="n">
-        <v>377.8375016176021</v>
+        <v>377.832961492048</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -20311,28 +20363,28 @@
         <v>0.1999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0478635581741647</v>
+        <v>-0.04654461731174235</v>
       </c>
       <c r="J4" t="n">
+        <v>373</v>
+      </c>
+      <c r="K4" t="n">
         <v>372</v>
       </c>
-      <c r="K4" t="n">
-        <v>371</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.01115437610657455</v>
+        <v>0.01060376093360427</v>
       </c>
       <c r="M4" t="n">
-        <v>2.575045405991116</v>
+        <v>2.573981417415418</v>
       </c>
       <c r="N4" t="n">
-        <v>10.73936001889467</v>
+        <v>10.72554871450529</v>
       </c>
       <c r="O4" t="n">
-        <v>3.277096278551283</v>
+        <v>3.274988353338878</v>
       </c>
       <c r="P4" t="n">
-        <v>378.2369433310558</v>
+        <v>378.2227362475484</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -20389,28 +20441,28 @@
         <v>0.0883</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0357549897502448</v>
+        <v>0.03676309763082945</v>
       </c>
       <c r="J5" t="n">
+        <v>373</v>
+      </c>
+      <c r="K5" t="n">
         <v>372</v>
       </c>
-      <c r="K5" t="n">
-        <v>371</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.004878530316499763</v>
+        <v>0.005184212714994141</v>
       </c>
       <c r="M5" t="n">
-        <v>2.883632074295874</v>
+        <v>2.880117172306125</v>
       </c>
       <c r="N5" t="n">
-        <v>13.78940832104399</v>
+        <v>13.76113690625409</v>
       </c>
       <c r="O5" t="n">
-        <v>3.713409258490638</v>
+        <v>3.709600639725803</v>
       </c>
       <c r="P5" t="n">
-        <v>376.0510886658736</v>
+        <v>376.0402297462267</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -20467,28 +20519,28 @@
         <v>0.1058</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06226448502523071</v>
+        <v>0.06388123269351403</v>
       </c>
       <c r="J6" t="n">
+        <v>373</v>
+      </c>
+      <c r="K6" t="n">
         <v>372</v>
       </c>
-      <c r="K6" t="n">
-        <v>371</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.02207970393084535</v>
+        <v>0.02329639151112772</v>
       </c>
       <c r="M6" t="n">
-        <v>2.371879953517094</v>
+        <v>2.37206062073768</v>
       </c>
       <c r="N6" t="n">
-        <v>9.079799176590628</v>
+        <v>9.078016682132704</v>
       </c>
       <c r="O6" t="n">
-        <v>3.013270511685041</v>
+        <v>3.012974723115463</v>
       </c>
       <c r="P6" t="n">
-        <v>372.061796209508</v>
+        <v>372.0443812747006</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -20545,28 +20597,28 @@
         <v>0.0876</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1230228061904929</v>
+        <v>0.1237212697643188</v>
       </c>
       <c r="J7" t="n">
+        <v>373</v>
+      </c>
+      <c r="K7" t="n">
         <v>372</v>
       </c>
-      <c r="K7" t="n">
-        <v>371</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.0451303235889825</v>
+        <v>0.04587666344498953</v>
       </c>
       <c r="M7" t="n">
-        <v>3.22446927266331</v>
+        <v>3.218032938775965</v>
       </c>
       <c r="N7" t="n">
-        <v>16.93293107716891</v>
+        <v>16.89163526480295</v>
       </c>
       <c r="O7" t="n">
-        <v>4.114964286256797</v>
+        <v>4.109943462482538</v>
       </c>
       <c r="P7" t="n">
-        <v>365.5226374397222</v>
+        <v>365.5151138800213</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -20623,28 +20675,28 @@
         <v>0.0589</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1205263196503963</v>
+        <v>-0.121033189932516</v>
       </c>
       <c r="J8" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K8" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03027901683967249</v>
+        <v>0.03070426392155379</v>
       </c>
       <c r="M8" t="n">
-        <v>3.900336939423952</v>
+        <v>3.892119259928837</v>
       </c>
       <c r="N8" t="n">
-        <v>24.8379722872074</v>
+        <v>24.77363825044626</v>
       </c>
       <c r="O8" t="n">
-        <v>4.983770890320642</v>
+        <v>4.977312352107939</v>
       </c>
       <c r="P8" t="n">
-        <v>369.1074515091232</v>
+        <v>369.1128759302579</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -20701,28 +20753,28 @@
         <v>0.0837</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.05719203484933316</v>
+        <v>-0.05761876221912304</v>
       </c>
       <c r="J9" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K9" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01097943567509596</v>
+        <v>0.01120814806793102</v>
       </c>
       <c r="M9" t="n">
-        <v>2.831071490429261</v>
+        <v>2.825242200406149</v>
       </c>
       <c r="N9" t="n">
-        <v>15.73054337197717</v>
+        <v>15.68996911424681</v>
       </c>
       <c r="O9" t="n">
-        <v>3.966174904360267</v>
+        <v>3.961056565393482</v>
       </c>
       <c r="P9" t="n">
-        <v>369.1151105739933</v>
+        <v>369.1196773222229</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -20779,28 +20831,28 @@
         <v>0.076</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.05311871513128841</v>
+        <v>-0.05332171374627876</v>
       </c>
       <c r="J10" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K10" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L10" t="n">
-        <v>0.006681227487688179</v>
+        <v>0.006772734917690926</v>
       </c>
       <c r="M10" t="n">
-        <v>3.626322562754534</v>
+        <v>3.61735639808522</v>
       </c>
       <c r="N10" t="n">
-        <v>22.39622546586588</v>
+        <v>22.33654377055067</v>
       </c>
       <c r="O10" t="n">
-        <v>4.732465051732118</v>
+        <v>4.726155284218946</v>
       </c>
       <c r="P10" t="n">
-        <v>366.712237150497</v>
+        <v>366.7144095997731</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -20857,28 +20909,28 @@
         <v>0.1273</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1365938293123805</v>
+        <v>-0.1389849712298641</v>
       </c>
       <c r="J11" t="n">
+        <v>373</v>
+      </c>
+      <c r="K11" t="n">
         <v>372</v>
       </c>
-      <c r="K11" t="n">
-        <v>371</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.06242613298935873</v>
+        <v>0.06465586925087097</v>
       </c>
       <c r="M11" t="n">
-        <v>3.145686741809387</v>
+        <v>3.149431111438885</v>
       </c>
       <c r="N11" t="n">
-        <v>14.81789282076567</v>
+        <v>14.82755071603278</v>
       </c>
       <c r="O11" t="n">
-        <v>3.849401618533154</v>
+        <v>3.850655881279549</v>
       </c>
       <c r="P11" t="n">
-        <v>381.2307274791533</v>
+        <v>381.2564838673795</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -20916,7 +20968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L373"/>
+  <dimension ref="A1:L374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44017,6 +44069,68 @@
         </is>
       </c>
     </row>
+    <row r="374">
+      <c r="A374" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>-36.72668131255622,175.70209922464832</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>-36.726635637462515,175.70299648358818</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>-36.72657701613851,175.7038903758694</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>-36.7265069530852,175.70477974193366</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>-36.72643122835495,175.70567081826886</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>-36.72639419077865,175.70657092785518</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>-36.72632644985365,175.7074660219252</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>-36.72617950672873,175.7083425963479</t>
+        </is>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>-36.7260371649365,175.70922442666998</t>
+        </is>
+      </c>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>-36.72585667912795,175.71009791272735</t>
+        </is>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0158/nzd0158.xlsx
+++ b/data/nzd0158/nzd0158.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L374"/>
+  <dimension ref="A1:L375"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16140,6 +16140,48 @@
         <v>373.29</v>
       </c>
       <c r="L374" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>382.86</v>
+      </c>
+      <c r="C375" t="n">
+        <v>379.55</v>
+      </c>
+      <c r="D375" t="n">
+        <v>379.26</v>
+      </c>
+      <c r="E375" t="n">
+        <v>378.73</v>
+      </c>
+      <c r="F375" t="n">
+        <v>376.58</v>
+      </c>
+      <c r="G375" t="n">
+        <v>370.13</v>
+      </c>
+      <c r="H375" t="n">
+        <v>365.88</v>
+      </c>
+      <c r="I375" t="n">
+        <v>367.21</v>
+      </c>
+      <c r="J375" t="n">
+        <v>365.81</v>
+      </c>
+      <c r="K375" t="n">
+        <v>375.27</v>
+      </c>
+      <c r="L375" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -16156,7 +16198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B388"/>
+  <dimension ref="A1:B389"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20039,6 +20081,16 @@
       </c>
       <c r="B388" t="n">
         <v>-0.08</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B389" t="n">
+        <v>-0.46</v>
       </c>
     </row>
   </sheetData>
@@ -20207,28 +20259,28 @@
         <v>0.109</v>
       </c>
       <c r="I2" t="n">
-        <v>0.12488654856879</v>
+        <v>0.124932921847337</v>
       </c>
       <c r="J2" t="n">
+        <v>374</v>
+      </c>
+      <c r="K2" t="n">
         <v>373</v>
       </c>
-      <c r="K2" t="n">
-        <v>372</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.04199135049454916</v>
+        <v>0.04226898939182355</v>
       </c>
       <c r="M2" t="n">
-        <v>3.436438295611768</v>
+        <v>3.427444126960499</v>
       </c>
       <c r="N2" t="n">
-        <v>18.88039948641866</v>
+        <v>18.82980038938317</v>
       </c>
       <c r="O2" t="n">
-        <v>4.345158165869069</v>
+        <v>4.339331790654313</v>
       </c>
       <c r="P2" t="n">
-        <v>379.4474070973187</v>
+        <v>379.446905800444</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -20285,28 +20337,28 @@
         <v>0.1104</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05344829856953776</v>
+        <v>0.05361128045069091</v>
       </c>
       <c r="J3" t="n">
+        <v>374</v>
+      </c>
+      <c r="K3" t="n">
         <v>373</v>
       </c>
-      <c r="K3" t="n">
-        <v>372</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.01182320753153432</v>
+        <v>0.01196671089442991</v>
       </c>
       <c r="M3" t="n">
-        <v>2.760248378862429</v>
+        <v>2.753666354616045</v>
       </c>
       <c r="N3" t="n">
-        <v>12.66885517639256</v>
+        <v>12.6351201175247</v>
       </c>
       <c r="O3" t="n">
-        <v>3.559333529804781</v>
+        <v>3.554591413583944</v>
       </c>
       <c r="P3" t="n">
-        <v>377.832961492048</v>
+        <v>377.8311996518199</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -20363,28 +20415,28 @@
         <v>0.1999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.04654461731174235</v>
+        <v>-0.0452840444172739</v>
       </c>
       <c r="J4" t="n">
+        <v>374</v>
+      </c>
+      <c r="K4" t="n">
         <v>373</v>
       </c>
-      <c r="K4" t="n">
-        <v>372</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.01060376093360427</v>
+        <v>0.01009124283749474</v>
       </c>
       <c r="M4" t="n">
-        <v>2.573981417415418</v>
+        <v>2.572617800364561</v>
       </c>
       <c r="N4" t="n">
-        <v>10.72554871450529</v>
+        <v>10.71053490910166</v>
       </c>
       <c r="O4" t="n">
-        <v>3.274988353338878</v>
+        <v>3.272695358431894</v>
       </c>
       <c r="P4" t="n">
-        <v>378.2227362475484</v>
+        <v>378.2091094074345</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -20441,28 +20493,28 @@
         <v>0.0883</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03676309763082945</v>
+        <v>0.03771371924254919</v>
       </c>
       <c r="J5" t="n">
+        <v>374</v>
+      </c>
+      <c r="K5" t="n">
         <v>373</v>
       </c>
-      <c r="K5" t="n">
-        <v>372</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.005184212714994141</v>
+        <v>0.005484598505017146</v>
       </c>
       <c r="M5" t="n">
-        <v>2.880117172306125</v>
+        <v>2.876343710147858</v>
       </c>
       <c r="N5" t="n">
-        <v>13.76113690625409</v>
+        <v>13.732058225923</v>
       </c>
       <c r="O5" t="n">
-        <v>3.709600639725803</v>
+        <v>3.705679185510127</v>
       </c>
       <c r="P5" t="n">
-        <v>376.0402297462267</v>
+        <v>376.0299534910664</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -20519,28 +20571,28 @@
         <v>0.1058</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06388123269351403</v>
+        <v>0.06545162090396082</v>
       </c>
       <c r="J6" t="n">
+        <v>374</v>
+      </c>
+      <c r="K6" t="n">
         <v>373</v>
       </c>
-      <c r="K6" t="n">
-        <v>372</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.02329639151112772</v>
+        <v>0.02451791368092548</v>
       </c>
       <c r="M6" t="n">
-        <v>2.37206062073768</v>
+        <v>2.371994532695095</v>
       </c>
       <c r="N6" t="n">
-        <v>9.078016682132704</v>
+        <v>9.07500422651105</v>
       </c>
       <c r="O6" t="n">
-        <v>3.012974723115463</v>
+        <v>3.012474767779981</v>
       </c>
       <c r="P6" t="n">
-        <v>372.0443812747006</v>
+        <v>372.0274053194391</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -20597,28 +20649,28 @@
         <v>0.0876</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1237212697643188</v>
+        <v>0.1244513597255406</v>
       </c>
       <c r="J7" t="n">
+        <v>374</v>
+      </c>
+      <c r="K7" t="n">
         <v>373</v>
       </c>
-      <c r="K7" t="n">
-        <v>372</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.04587666344498953</v>
+        <v>0.04665467372157017</v>
       </c>
       <c r="M7" t="n">
-        <v>3.218032938775965</v>
+        <v>3.211739833512959</v>
       </c>
       <c r="N7" t="n">
-        <v>16.89163526480295</v>
+        <v>16.85095868704595</v>
       </c>
       <c r="O7" t="n">
-        <v>4.109943462482538</v>
+        <v>4.104991922896555</v>
       </c>
       <c r="P7" t="n">
-        <v>365.5151138800213</v>
+        <v>365.5072215802473</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -20675,28 +20727,28 @@
         <v>0.0589</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.121033189932516</v>
+        <v>-0.1210377614627477</v>
       </c>
       <c r="J8" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K8" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03070426392155379</v>
+        <v>0.03088888628762465</v>
       </c>
       <c r="M8" t="n">
-        <v>3.892119259928837</v>
+        <v>3.881732496019574</v>
       </c>
       <c r="N8" t="n">
-        <v>24.77363825044626</v>
+        <v>24.70739875928619</v>
       </c>
       <c r="O8" t="n">
-        <v>4.977312352107939</v>
+        <v>4.970653755723304</v>
       </c>
       <c r="P8" t="n">
-        <v>369.1128759302579</v>
+        <v>369.1129250299626</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -20753,28 +20805,28 @@
         <v>0.0837</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.05761876221912304</v>
+        <v>-0.05782241363184914</v>
       </c>
       <c r="J9" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K9" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01120814806793102</v>
+        <v>0.01135474637124412</v>
       </c>
       <c r="M9" t="n">
-        <v>2.825242200406149</v>
+        <v>2.81851885459114</v>
       </c>
       <c r="N9" t="n">
-        <v>15.68996911424681</v>
+        <v>15.64838109709891</v>
       </c>
       <c r="O9" t="n">
-        <v>3.961056565393482</v>
+        <v>3.955803470484714</v>
       </c>
       <c r="P9" t="n">
-        <v>369.1196773222229</v>
+        <v>369.1218646038776</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -20831,28 +20883,28 @@
         <v>0.076</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.05332171374627876</v>
+        <v>-0.05303481287651144</v>
       </c>
       <c r="J10" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K10" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L10" t="n">
-        <v>0.006772734917690926</v>
+        <v>0.006741106682087605</v>
       </c>
       <c r="M10" t="n">
-        <v>3.61735639808522</v>
+        <v>3.609395700850151</v>
       </c>
       <c r="N10" t="n">
-        <v>22.33654377055067</v>
+        <v>22.27754235966494</v>
       </c>
       <c r="O10" t="n">
-        <v>4.726155284218946</v>
+        <v>4.719909147395206</v>
       </c>
       <c r="P10" t="n">
-        <v>366.7144095997731</v>
+        <v>366.7113281921819</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -20909,28 +20961,28 @@
         <v>0.1273</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1389849712298641</v>
+        <v>-0.1402498660059425</v>
       </c>
       <c r="J11" t="n">
+        <v>374</v>
+      </c>
+      <c r="K11" t="n">
         <v>373</v>
       </c>
-      <c r="K11" t="n">
-        <v>372</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.06465586925087097</v>
+        <v>0.06608072869391612</v>
       </c>
       <c r="M11" t="n">
-        <v>3.149431111438885</v>
+        <v>3.147428995318541</v>
       </c>
       <c r="N11" t="n">
-        <v>14.82755071603278</v>
+        <v>14.80163397006418</v>
       </c>
       <c r="O11" t="n">
-        <v>3.850655881279549</v>
+        <v>3.847289171619957</v>
       </c>
       <c r="P11" t="n">
-        <v>381.2564838673795</v>
+        <v>381.2701574271951</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -20968,7 +21020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L374"/>
+  <dimension ref="A1:L375"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44131,6 +44183,68 @@
         </is>
       </c>
     </row>
+    <row r="375">
+      <c r="A375" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>-36.726674954371234,175.7020983624834</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>-36.72663975684526,175.70299704220463</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>-36.72657773195468,175.70389047959873</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>-36.726507756158526,175.70477988023356</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>-36.72643167357131,175.70567090306218</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>-36.726393479833604,175.7065707812843</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>-36.72631848746585,175.70746412475168</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>-36.72617607939202,175.70834163702582</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>-36.72602940112055,175.7092224367158</t>
+        </is>
+      </c>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>-36.72583908784306,175.7100942510583</t>
+        </is>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0158/nzd0158.xlsx
+++ b/data/nzd0158/nzd0158.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L375"/>
+  <dimension ref="A1:L377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16184,6 +16184,90 @@
       <c r="L375" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>388</v>
+      </c>
+      <c r="C376" t="n">
+        <v>381.74</v>
+      </c>
+      <c r="D376" t="n">
+        <v>379.39</v>
+      </c>
+      <c r="E376" t="n">
+        <v>383.09</v>
+      </c>
+      <c r="F376" t="n">
+        <v>377.93</v>
+      </c>
+      <c r="G376" t="n">
+        <v>370.78</v>
+      </c>
+      <c r="H376" t="n">
+        <v>368.6</v>
+      </c>
+      <c r="I376" t="n">
+        <v>371.14</v>
+      </c>
+      <c r="J376" t="n">
+        <v>368.62</v>
+      </c>
+      <c r="K376" t="n">
+        <v>379.88</v>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:04:56+00:00</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>387.13</v>
+      </c>
+      <c r="C377" t="n">
+        <v>380.5</v>
+      </c>
+      <c r="D377" t="n">
+        <v>379.31</v>
+      </c>
+      <c r="E377" t="n">
+        <v>380.82</v>
+      </c>
+      <c r="F377" t="n">
+        <v>376.84</v>
+      </c>
+      <c r="G377" t="n">
+        <v>369.47</v>
+      </c>
+      <c r="H377" t="n">
+        <v>368.4</v>
+      </c>
+      <c r="I377" t="n">
+        <v>369.68</v>
+      </c>
+      <c r="J377" t="n">
+        <v>366.38</v>
+      </c>
+      <c r="K377" t="n">
+        <v>379.73</v>
+      </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -16198,7 +16282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B389"/>
+  <dimension ref="A1:B391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20091,6 +20175,26 @@
       </c>
       <c r="B389" t="n">
         <v>-0.46</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B390" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B391" t="n">
+        <v>-0.62</v>
       </c>
     </row>
   </sheetData>
@@ -20259,28 +20363,28 @@
         <v>0.109</v>
       </c>
       <c r="I2" t="n">
-        <v>0.124932921847337</v>
+        <v>0.1302072822663362</v>
       </c>
       <c r="J2" t="n">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="K2" t="n">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04226898939182355</v>
+        <v>0.04601352810044868</v>
       </c>
       <c r="M2" t="n">
-        <v>3.427444126960499</v>
+        <v>3.433928277242303</v>
       </c>
       <c r="N2" t="n">
-        <v>18.82980038938317</v>
+        <v>18.84923824364506</v>
       </c>
       <c r="O2" t="n">
-        <v>4.339331790654313</v>
+        <v>4.341570941910896</v>
       </c>
       <c r="P2" t="n">
-        <v>379.446905800444</v>
+        <v>379.3894678951693</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -20337,28 +20441,28 @@
         <v>0.1104</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05361128045069091</v>
+        <v>0.05566179419838314</v>
       </c>
       <c r="J3" t="n">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="K3" t="n">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01196671089442991</v>
+        <v>0.01302680535395528</v>
       </c>
       <c r="M3" t="n">
-        <v>2.753666354616045</v>
+        <v>2.74905421409199</v>
       </c>
       <c r="N3" t="n">
-        <v>12.6351201175247</v>
+        <v>12.58775870965556</v>
       </c>
       <c r="O3" t="n">
-        <v>3.554591413583944</v>
+        <v>3.547923154418027</v>
       </c>
       <c r="P3" t="n">
-        <v>377.8311996518199</v>
+        <v>377.8088718727238</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -20415,28 +20519,28 @@
         <v>0.1999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0452840444172739</v>
+        <v>-0.04267538744568741</v>
       </c>
       <c r="J4" t="n">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="K4" t="n">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01009124283749474</v>
+        <v>0.009059344925532398</v>
       </c>
       <c r="M4" t="n">
-        <v>2.572617800364561</v>
+        <v>2.570169850480208</v>
       </c>
       <c r="N4" t="n">
-        <v>10.71053490910166</v>
+        <v>10.68248692256395</v>
       </c>
       <c r="O4" t="n">
-        <v>3.272695358431894</v>
+        <v>3.268407398499145</v>
       </c>
       <c r="P4" t="n">
-        <v>378.2091094074345</v>
+        <v>378.1807001487756</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -20493,28 +20597,28 @@
         <v>0.0883</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03771371924254919</v>
+        <v>0.04315519817298894</v>
       </c>
       <c r="J5" t="n">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="K5" t="n">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="L5" t="n">
-        <v>0.005484598505017146</v>
+        <v>0.007188924193072155</v>
       </c>
       <c r="M5" t="n">
-        <v>2.876343710147858</v>
+        <v>2.883229853367215</v>
       </c>
       <c r="N5" t="n">
-        <v>13.732058225923</v>
+        <v>13.79226246922007</v>
       </c>
       <c r="O5" t="n">
-        <v>3.705679185510127</v>
+        <v>3.713793541544827</v>
       </c>
       <c r="P5" t="n">
-        <v>376.0299534910664</v>
+        <v>375.9706992628587</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -20571,28 +20675,28 @@
         <v>0.1058</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06545162090396082</v>
+        <v>0.06943540260829245</v>
       </c>
       <c r="J6" t="n">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="K6" t="n">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02451791368092548</v>
+        <v>0.02763795803167457</v>
       </c>
       <c r="M6" t="n">
-        <v>2.371994532695095</v>
+        <v>2.375375094180893</v>
       </c>
       <c r="N6" t="n">
-        <v>9.07500422651105</v>
+        <v>9.096001707883637</v>
       </c>
       <c r="O6" t="n">
-        <v>3.012474767779981</v>
+        <v>3.015957842524268</v>
       </c>
       <c r="P6" t="n">
-        <v>372.0274053194391</v>
+        <v>371.9840229753709</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -20649,28 +20753,28 @@
         <v>0.0876</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1244513597255406</v>
+        <v>0.1258661061395194</v>
       </c>
       <c r="J7" t="n">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="K7" t="n">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04665467372157017</v>
+        <v>0.04821057178691712</v>
       </c>
       <c r="M7" t="n">
-        <v>3.211739833512959</v>
+        <v>3.199028016235853</v>
       </c>
       <c r="N7" t="n">
-        <v>16.85095868704595</v>
+        <v>16.77191918998603</v>
       </c>
       <c r="O7" t="n">
-        <v>4.104991922896555</v>
+        <v>4.09535336570436</v>
       </c>
       <c r="P7" t="n">
-        <v>365.5072215802473</v>
+        <v>365.4918177683483</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -20727,28 +20831,28 @@
         <v>0.0589</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1210377614627477</v>
+        <v>-0.1181431766776839</v>
       </c>
       <c r="J8" t="n">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="K8" t="n">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03088888628762465</v>
+        <v>0.02978672698750162</v>
       </c>
       <c r="M8" t="n">
-        <v>3.881732496019574</v>
+        <v>3.87634012723474</v>
       </c>
       <c r="N8" t="n">
-        <v>24.70739875928619</v>
+        <v>24.61232761170567</v>
       </c>
       <c r="O8" t="n">
-        <v>4.970653755723304</v>
+        <v>4.961081294607625</v>
       </c>
       <c r="P8" t="n">
-        <v>369.1129250299626</v>
+        <v>369.0816035043162</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -20805,28 +20909,28 @@
         <v>0.0837</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.05782241363184914</v>
+        <v>-0.05470172712230542</v>
       </c>
       <c r="J9" t="n">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="K9" t="n">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01135474637124412</v>
+        <v>0.01027074084797119</v>
       </c>
       <c r="M9" t="n">
-        <v>2.81851885459114</v>
+        <v>2.820894828906686</v>
       </c>
       <c r="N9" t="n">
-        <v>15.64838109709891</v>
+        <v>15.61017198112737</v>
       </c>
       <c r="O9" t="n">
-        <v>3.955803470484714</v>
+        <v>3.950971017500302</v>
       </c>
       <c r="P9" t="n">
-        <v>369.1218646038776</v>
+        <v>369.0880997409807</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -20883,28 +20987,28 @@
         <v>0.076</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.05303481287651144</v>
+        <v>-0.05061136195843965</v>
       </c>
       <c r="J10" t="n">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="K10" t="n">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="L10" t="n">
-        <v>0.006741106682087605</v>
+        <v>0.0062101386900838</v>
       </c>
       <c r="M10" t="n">
-        <v>3.609395700850151</v>
+        <v>3.604374352317872</v>
       </c>
       <c r="N10" t="n">
-        <v>22.27754235966494</v>
+        <v>22.19117423752193</v>
       </c>
       <c r="O10" t="n">
-        <v>4.719909147395206</v>
+        <v>4.71075092076857</v>
       </c>
       <c r="P10" t="n">
-        <v>366.7113281921819</v>
+        <v>366.6851100902233</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -20961,28 +21065,28 @@
         <v>0.1273</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1402498660059425</v>
+        <v>-0.1377021430371886</v>
       </c>
       <c r="J11" t="n">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="K11" t="n">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="L11" t="n">
-        <v>0.06608072869391612</v>
+        <v>0.06448984880244646</v>
       </c>
       <c r="M11" t="n">
-        <v>3.147428995318541</v>
+        <v>3.142073951502272</v>
       </c>
       <c r="N11" t="n">
-        <v>14.80163397006418</v>
+        <v>14.75044481818857</v>
       </c>
       <c r="O11" t="n">
-        <v>3.847289171619957</v>
+        <v>3.840630783893261</v>
       </c>
       <c r="P11" t="n">
-        <v>381.2701574271951</v>
+        <v>381.2424119354081</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -21020,7 +21124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L375"/>
+  <dimension ref="A1:L377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44245,6 +44349,130 @@
         </is>
       </c>
     </row>
+    <row r="376">
+      <c r="A376" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>-36.7266289246935,175.7020921209003</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>-36.726620145001185,175.70299438270519</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>-36.72657656875341,175.70389031103858</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>-36.726468851716646,175.7047731803754</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>-36.726419652729064,175.70566861364313</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>-36.726387703405,175.70656959039596</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>-36.726294423360166,175.70745839107434</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>-36.726141542382976,175.70833197001636</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>-36.726004609844246,175.70921608243324</t>
+        </is>
+      </c>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>-36.72579813035563,175.71008572566464</t>
+        </is>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:04:56+00:00</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>-36.72663671570907,175.70209317735436</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>-36.726631249424344,175.7029958885403</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>-36.72657728456958,175.7038904147679</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>-36.726489107011034,175.70477666860333</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>-36.72642935844615,175.70567046213696</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>-36.726399345130304,175.70657199049424</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>-36.726296192779714,175.70745881266814</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>-36.726154372925926,175.70833556132155</t>
+        </is>
+      </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>-36.726024372285195,175.70922114776843</t>
+        </is>
+      </c>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>-36.725799463028764,175.7100860030634</t>
+        </is>
+      </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0158/nzd0158.xlsx
+++ b/data/nzd0158/nzd0158.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L377"/>
+  <dimension ref="A1:L378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16266,6 +16266,48 @@
         <v>379.73</v>
       </c>
       <c r="L377" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B378" t="n">
+        <v>386.71</v>
+      </c>
+      <c r="C378" t="n">
+        <v>380.4</v>
+      </c>
+      <c r="D378" t="n">
+        <v>381.59</v>
+      </c>
+      <c r="E378" t="n">
+        <v>381.21</v>
+      </c>
+      <c r="F378" t="n">
+        <v>377.07</v>
+      </c>
+      <c r="G378" t="n">
+        <v>371.38</v>
+      </c>
+      <c r="H378" t="n">
+        <v>369.15</v>
+      </c>
+      <c r="I378" t="n">
+        <v>370.13</v>
+      </c>
+      <c r="J378" t="n">
+        <v>366.98</v>
+      </c>
+      <c r="K378" t="n">
+        <v>381.25</v>
+      </c>
+      <c r="L378" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -16282,7 +16324,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B391"/>
+  <dimension ref="A1:B392"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20195,6 +20237,16 @@
       </c>
       <c r="B391" t="n">
         <v>-0.62</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B392" t="n">
+        <v>-0.6</v>
       </c>
     </row>
   </sheetData>
@@ -20363,28 +20415,28 @@
         <v>0.109</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1302072822663362</v>
+        <v>0.1323125401419989</v>
       </c>
       <c r="J2" t="n">
+        <v>377</v>
+      </c>
+      <c r="K2" t="n">
         <v>376</v>
       </c>
-      <c r="K2" t="n">
-        <v>375</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.04601352810044868</v>
+        <v>0.04763028459752039</v>
       </c>
       <c r="M2" t="n">
-        <v>3.433928277242303</v>
+        <v>3.435178838696747</v>
       </c>
       <c r="N2" t="n">
-        <v>18.84923824364506</v>
+        <v>18.83750882209141</v>
       </c>
       <c r="O2" t="n">
-        <v>4.341570941910896</v>
+        <v>4.340219904807982</v>
       </c>
       <c r="P2" t="n">
-        <v>379.3894678951693</v>
+        <v>379.3664910660457</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -20441,28 +20493,28 @@
         <v>0.1104</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05566179419838314</v>
+        <v>0.0562679956049555</v>
       </c>
       <c r="J3" t="n">
+        <v>377</v>
+      </c>
+      <c r="K3" t="n">
         <v>376</v>
       </c>
-      <c r="K3" t="n">
-        <v>375</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.01302680535395528</v>
+        <v>0.01338649976031836</v>
       </c>
       <c r="M3" t="n">
-        <v>2.74905421409199</v>
+        <v>2.744697810095876</v>
       </c>
       <c r="N3" t="n">
-        <v>12.58775870965556</v>
+        <v>12.55746461889548</v>
       </c>
       <c r="O3" t="n">
-        <v>3.547923154418027</v>
+        <v>3.543651311697509</v>
       </c>
       <c r="P3" t="n">
-        <v>377.8088718727238</v>
+        <v>377.8022557777103</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -20519,28 +20571,28 @@
         <v>0.1999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.04267538744568741</v>
+        <v>-0.04016173518454366</v>
       </c>
       <c r="J4" t="n">
+        <v>377</v>
+      </c>
+      <c r="K4" t="n">
         <v>376</v>
       </c>
-      <c r="K4" t="n">
-        <v>375</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.009059344925532398</v>
+        <v>0.00804037501007937</v>
       </c>
       <c r="M4" t="n">
-        <v>2.570169850480208</v>
+        <v>2.574611360532436</v>
       </c>
       <c r="N4" t="n">
-        <v>10.68248692256395</v>
+        <v>10.70882154150361</v>
       </c>
       <c r="O4" t="n">
-        <v>3.268407398499145</v>
+        <v>3.272433580915526</v>
       </c>
       <c r="P4" t="n">
-        <v>378.1807001487756</v>
+        <v>378.1532660946638</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -20597,28 +20649,28 @@
         <v>0.0883</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04315519817298894</v>
+        <v>0.04540488610469795</v>
       </c>
       <c r="J5" t="n">
+        <v>377</v>
+      </c>
+      <c r="K5" t="n">
         <v>376</v>
       </c>
-      <c r="K5" t="n">
-        <v>375</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.007188924193072155</v>
+        <v>0.007975636568990696</v>
       </c>
       <c r="M5" t="n">
-        <v>2.883229853367215</v>
+        <v>2.884683395610538</v>
       </c>
       <c r="N5" t="n">
-        <v>13.79226246922007</v>
+        <v>13.79943222259317</v>
       </c>
       <c r="O5" t="n">
-        <v>3.713793541544827</v>
+        <v>3.714758703145221</v>
       </c>
       <c r="P5" t="n">
-        <v>375.9706992628587</v>
+        <v>375.9461461210388</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -20675,28 +20727,28 @@
         <v>0.1058</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06943540260829245</v>
+        <v>0.07121246858808296</v>
       </c>
       <c r="J6" t="n">
+        <v>377</v>
+      </c>
+      <c r="K6" t="n">
         <v>376</v>
       </c>
-      <c r="K6" t="n">
-        <v>375</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.02763795803167457</v>
+        <v>0.02911892223362145</v>
       </c>
       <c r="M6" t="n">
-        <v>2.375375094180893</v>
+        <v>2.376488751548587</v>
       </c>
       <c r="N6" t="n">
-        <v>9.096001707883637</v>
+        <v>9.099172038037805</v>
       </c>
       <c r="O6" t="n">
-        <v>3.015957842524268</v>
+        <v>3.01648338931906</v>
       </c>
       <c r="P6" t="n">
-        <v>371.9840229753709</v>
+        <v>371.9646280395623</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -20753,28 +20805,28 @@
         <v>0.0876</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1258661061395194</v>
+        <v>0.1272466223066714</v>
       </c>
       <c r="J7" t="n">
+        <v>377</v>
+      </c>
+      <c r="K7" t="n">
         <v>376</v>
       </c>
-      <c r="K7" t="n">
-        <v>375</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.04821057178691712</v>
+        <v>0.04946575589131241</v>
       </c>
       <c r="M7" t="n">
-        <v>3.199028016235853</v>
+        <v>3.194785497203114</v>
       </c>
       <c r="N7" t="n">
-        <v>16.77191918998603</v>
+        <v>16.74382583004645</v>
       </c>
       <c r="O7" t="n">
-        <v>4.09535336570436</v>
+        <v>4.091922021501198</v>
       </c>
       <c r="P7" t="n">
-        <v>365.4918177683483</v>
+        <v>365.4767507856087</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -20831,28 +20883,28 @@
         <v>0.0589</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1181431766776839</v>
+        <v>-0.1163685810598138</v>
       </c>
       <c r="J8" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K8" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02978672698750162</v>
+        <v>0.02906608583087689</v>
       </c>
       <c r="M8" t="n">
-        <v>3.87634012723474</v>
+        <v>3.875359797143998</v>
       </c>
       <c r="N8" t="n">
-        <v>24.61232761170567</v>
+        <v>24.57471829347251</v>
       </c>
       <c r="O8" t="n">
-        <v>4.961081294607625</v>
+        <v>4.957289409896553</v>
       </c>
       <c r="P8" t="n">
-        <v>369.0816035043162</v>
+        <v>369.06235887427</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -20909,28 +20961,28 @@
         <v>0.0837</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.05470172712230542</v>
+        <v>-0.05332707470669139</v>
       </c>
       <c r="J9" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K9" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01027074084797119</v>
+        <v>0.009815410231346022</v>
       </c>
       <c r="M9" t="n">
-        <v>2.820894828906686</v>
+        <v>2.821163930983635</v>
       </c>
       <c r="N9" t="n">
-        <v>15.61017198112737</v>
+        <v>15.58537227818014</v>
       </c>
       <c r="O9" t="n">
-        <v>3.950971017500302</v>
+        <v>3.947831338618729</v>
       </c>
       <c r="P9" t="n">
-        <v>369.0880997409807</v>
+        <v>369.0731923012721</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -20987,28 +21039,28 @@
         <v>0.076</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.05061136195843965</v>
+        <v>-0.04970457001040161</v>
       </c>
       <c r="J10" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K10" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0062101386900838</v>
+        <v>0.006025778486510869</v>
       </c>
       <c r="M10" t="n">
-        <v>3.604374352317872</v>
+        <v>3.60007944950828</v>
       </c>
       <c r="N10" t="n">
-        <v>22.19117423752193</v>
+        <v>22.1395379058099</v>
       </c>
       <c r="O10" t="n">
-        <v>4.71075092076857</v>
+        <v>4.705267038735411</v>
       </c>
       <c r="P10" t="n">
-        <v>366.6851100902233</v>
+        <v>366.6752763707026</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -21065,28 +21117,28 @@
         <v>0.1273</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1377021430371886</v>
+        <v>-0.135655948600065</v>
       </c>
       <c r="J11" t="n">
+        <v>377</v>
+      </c>
+      <c r="K11" t="n">
         <v>376</v>
       </c>
-      <c r="K11" t="n">
-        <v>375</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.06448984880244646</v>
+        <v>0.06292631690650985</v>
       </c>
       <c r="M11" t="n">
-        <v>3.142073951502272</v>
+        <v>3.142956226930814</v>
       </c>
       <c r="N11" t="n">
-        <v>14.75044481818857</v>
+        <v>14.74749194304995</v>
       </c>
       <c r="O11" t="n">
-        <v>3.840630783893261</v>
+        <v>3.840246338849886</v>
       </c>
       <c r="P11" t="n">
-        <v>381.2424119354081</v>
+        <v>381.2200797259059</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -21124,7 +21176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L377"/>
+  <dimension ref="A1:L378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44473,6 +44525,68 @@
         </is>
       </c>
     </row>
+    <row r="378">
+      <c r="A378" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>-36.726640476888974,175.70209368736676</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>-36.72663214494233,175.70299600997862</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>-36.726556883808755,175.70388745848336</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>-36.72648562702655,175.7047760693041</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>-36.72642731045081,175.70567007208774</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>-36.726382371317044,175.7065684911146</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>-36.72628955745639,175.70745723169156</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>-36.72615041830655,175.70833445441227</t>
+        </is>
+      </c>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>-36.72601907877427,175.70921979098193</t>
+        </is>
+      </c>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>-36.725785958607496,175.7100831920898</t>
+        </is>
+      </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
